--- a/Excel/Credit Cards.xlsx
+++ b/Excel/Credit Cards.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\A4\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2868A320-CD07-4CE9-AB15-8C257570700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2868A320-CD07-4CE9-AB15-8C257570700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{355C297A-06C0-4B67-93BC-1183D181E722}"/>
   <bookViews>
-    <workbookView xWindow="4848" yWindow="876" windowWidth="18000" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6540" yWindow="876" windowWidth="16260" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
   <si>
     <t>Bank</t>
   </si>
@@ -113,16 +113,10 @@
     <t>VISA 9113</t>
   </si>
   <si>
-    <t>TRUE INTERNET</t>
-  </si>
-  <si>
     <t>iCloud+</t>
   </si>
   <si>
     <t>YouTube Music</t>
-  </si>
-  <si>
-    <t>EverNote</t>
   </si>
   <si>
     <t>5444 8800 0134 3118</t>
@@ -281,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -321,7 +315,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -427,7 +421,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -569,7 +563,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -577,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.69921875" style="2" bestFit="1" customWidth="1"/>
@@ -711,7 +705,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="3">
-        <v>640.92999999999995</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -719,292 +713,272 @@
         <v>26</v>
       </c>
       <c r="D13" s="3">
-        <v>35</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="3">
-        <v>209</v>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="3">
-        <v>149</v>
-      </c>
-      <c r="E15" s="3">
-        <f>SUM(D12:D15)</f>
-        <v>1033.9299999999998</v>
+        <v>31</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>30</v>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3">
+        <v>3601.31</v>
+      </c>
+      <c r="G22" s="3">
+        <v>568371.43999999994</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C23" s="3"/>
+      <c r="A23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3">
+        <v>3504.09</v>
+      </c>
+      <c r="G23" s="3">
+        <v>613347.87</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="D24" s="3">
+        <v>50000</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3">
-        <v>3601.31</v>
+        <f>SUM(F22:F23)</f>
+        <v>7105.4</v>
       </c>
       <c r="G24" s="3">
-        <v>341268.09</v>
+        <f>G22+G23</f>
+        <v>1181719.31</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3">
-        <v>3504.09</v>
-      </c>
-      <c r="G25" s="3">
-        <v>608647.87</v>
+      <c r="D25" s="3">
+        <v>30000</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>43</v>
+        <v>4</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>141717.12</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3">
-        <f>SUM(F24:F25)</f>
-        <v>7105.4</v>
-      </c>
-      <c r="G26" s="3">
-        <f>G24+G25</f>
-        <v>949915.96</v>
-      </c>
+        <v>200000</v>
+      </c>
+      <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="3">
-        <v>100729.27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="3">
-        <v>105450.98</v>
-      </c>
-      <c r="G28" s="3"/>
+      <c r="C27" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="2">
+        <v>312</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="2" t="s">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>47</v>
+      </c>
+      <c r="C30" s="2">
+        <v>876</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C31" s="2">
-        <v>312</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>8</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="C32" s="2">
-        <v>876</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>50</v>
+        <v>453</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C33" s="2">
-        <v>944</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="6" t="s">
         <v>52</v>
       </c>
+      <c r="B34" s="3">
+        <v>300000</v>
+      </c>
       <c r="C34" s="2">
-        <v>453</v>
+        <v>67</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="A35" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B35" s="3">
         <v>300000</v>
       </c>
-      <c r="C36" s="2">
-        <v>67</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="C35" s="2">
+        <v>68</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="3">
-        <v>300000</v>
-      </c>
-      <c r="C37" s="2">
-        <v>68</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Credit Cards.xlsx
+++ b/Excel/Credit Cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2868A320-CD07-4CE9-AB15-8C257570700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{355C297A-06C0-4B67-93BC-1183D181E722}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{2868A320-CD07-4CE9-AB15-8C257570700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A565830-4639-4E7D-AB7A-FE97D804D498}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="876" windowWidth="16260" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3876" yWindow="780" windowWidth="18216" windowHeight="11364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="56">
   <si>
     <t>Bank</t>
   </si>
@@ -176,9 +176,6 @@
     <t>NAPAPORN</t>
   </si>
   <si>
-    <t>02 638 4000</t>
-  </si>
-  <si>
     <t>4546 3200 5140 9113</t>
   </si>
   <si>
@@ -188,12 +185,6 @@
     <t>4050 1630 0229 3121</t>
   </si>
   <si>
-    <t>5224 4060 0016 7980</t>
-  </si>
-  <si>
-    <t>Password of Citi mobile app = chutima14</t>
-  </si>
-  <si>
     <t>JMART</t>
   </si>
   <si>
@@ -204,6 +195,15 @@
   </si>
   <si>
     <t>APR</t>
+  </si>
+  <si>
+    <t>0626926112 Dtac Harassment</t>
+  </si>
+  <si>
+    <t>07/31</t>
+  </si>
+  <si>
+    <t>08/29</t>
   </si>
 </sst>
 </file>
@@ -249,14 +249,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -274,10 +273,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -315,7 +318,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -421,7 +424,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -563,7 +566,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -571,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.69921875" style="2" bestFit="1" customWidth="1"/>
@@ -814,10 +817,10 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3">
-        <v>3601.31</v>
+        <v>3521.94</v>
       </c>
       <c r="G22" s="3">
-        <v>568371.43999999994</v>
+        <v>371893.38</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -829,10 +832,10 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3">
-        <v>3504.09</v>
+        <v>3603.03</v>
       </c>
       <c r="G23" s="3">
-        <v>613347.87</v>
+        <v>619650.9</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -848,11 +851,11 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3">
         <f>SUM(F22:F23)</f>
-        <v>7105.4</v>
+        <v>7124.97</v>
       </c>
       <c r="G24" s="3">
         <f>G22+G23</f>
-        <v>1181719.31</v>
+        <v>991544.28</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -897,13 +900,13 @@
         <v>27</v>
       </c>
       <c r="C29" s="2">
-        <v>312</v>
+        <v>212</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -911,13 +914,16 @@
         <v>11</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="2">
+        <v>335</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="2">
-        <v>876</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>48</v>
+      <c r="E30" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -925,60 +931,46 @@
         <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2">
         <v>944</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="3">
+        <v>300000</v>
+      </c>
+      <c r="C32" s="2">
+        <v>67</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="2">
-        <v>453</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="B33" s="3">
+        <v>300000</v>
+      </c>
+      <c r="C33" s="2">
+        <v>68</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="3">
-        <v>300000</v>
-      </c>
-      <c r="C34" s="2">
-        <v>67</v>
-      </c>
-      <c r="D34" s="3" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B36" s="2" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="3">
-        <v>300000</v>
-      </c>
-      <c r="C35" s="2">
-        <v>68</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
